--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484661_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484661_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5516</v>
+        <v>7.7139</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5663</v>
+        <v>4.679</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9853</v>
+        <v>3.0349</v>
       </c>
       <c r="G2" t="n">
         <v>3.5864</v>
@@ -610,13 +610,13 @@
         <v>3.6651</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7</v>
+        <v>0.4623</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8265</v>
+        <v>0.2862</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1265</v>
+        <v>0.1761</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2313</v>
+        <v>5.1354</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0393</v>
+        <v>3.8444</v>
       </c>
       <c r="F3" t="n">
-        <v>1.192</v>
+        <v>1.2911</v>
       </c>
       <c r="G3" t="n">
         <v>2.9211</v>
@@ -688,13 +688,13 @@
         <v>2.9321</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8783</v>
+        <v>0.7824</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0672</v>
+        <v>0.8722</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1889</v>
+        <v>-0.0898</v>
       </c>
       <c r="V3" t="n">
         <v>0.3324</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0202</v>
+        <v>4.16</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2356</v>
+        <v>1.5241</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7846</v>
+        <v>2.6359</v>
       </c>
       <c r="G4" t="n">
         <v>1.9902</v>
@@ -766,13 +766,13 @@
         <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2266</v>
+        <v>-0.0867</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4962</v>
+        <v>-0.2077</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2697</v>
+        <v>0.121</v>
       </c>
       <c r="V4" t="n">
         <v>1.89</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2317</v>
+        <v>3.0679</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4483</v>
+        <v>1.0572</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6801</v>
+        <v>2.0107</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8652</v>
+        <v>2.2125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5095</v>
+        <v>2.2993</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3557</v>
+        <v>-0.0868</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08260000000000001</v>
+        <v>2.506</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0151</v>
+        <v>2.4643</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0674</v>
+        <v>0.0417</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7827</v>
+        <v>-0.2935</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4944</v>
+        <v>-0.165</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2882</v>
+        <v>-0.1285</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9321</v>
+        <v>3.1154</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.1054</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0347</v>
+        <v>0.0619</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0347</v>
+        <v>-0.1673</v>
       </c>
       <c r="V5" t="n">
-        <v>1.267</v>
+        <v>-0.3219</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8013</v>
+        <v>3.0394</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8649</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9364</v>
+        <v>3.6801</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2125</v>
+        <v>0.8652</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2993</v>
+        <v>0.5095</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0868</v>
+        <v>0.3557</v>
       </c>
       <c r="J6" t="n">
-        <v>2.506</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4643</v>
+        <v>0.0151</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0417</v>
+        <v>0.0674</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2935</v>
+        <v>0.7827</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.165</v>
+        <v>0.4944</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1285</v>
+        <v>0.2882</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1154</v>
+        <v>2.9321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.372</v>
+        <v>-0.1923</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1304</v>
+        <v>-0.1576</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2416</v>
+        <v>-0.0347</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4852</v>
+        <v>0.1606</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6347</v>
+        <v>1.7553</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1495</v>
+        <v>-1.5947</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3002</v>
+        <v>-0.8863</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.563</v>
+        <v>-1.8063</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2628</v>
+        <v>0.92</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.0073</v>
+        <v>1.692</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.174</v>
+        <v>0.291</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1667</v>
+        <v>1.401</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2929</v>
+        <v>-2.5783</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.389</v>
+        <v>-2.0973</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0961</v>
+        <v>-0.481</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4661</v>
+        <v>2.5656</v>
       </c>
       <c r="S7" t="n">
-        <v>1.349</v>
+        <v>0.3426</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3726</v>
+        <v>0.6576</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0236</v>
+        <v>-0.3151</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7931</v>
+        <v>-0.9738</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8759</v>
+        <v>-1.1977</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.669</v>
+        <v>0.2239</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8863</v>
+        <v>-3.3002</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8063</v>
+        <v>-3.563</v>
       </c>
       <c r="I8" t="n">
-        <v>0.92</v>
+        <v>0.2628</v>
       </c>
       <c r="J8" t="n">
-        <v>1.692</v>
+        <v>-2.0073</v>
       </c>
       <c r="K8" t="n">
-        <v>0.291</v>
+        <v>-2.174</v>
       </c>
       <c r="L8" t="n">
-        <v>1.401</v>
+        <v>0.1667</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5783</v>
+        <v>-1.2929</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0973</v>
+        <v>-1.389</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.481</v>
+        <v>0.0961</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6111</v>
+        <v>0.8603</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2217</v>
+        <v>0.8096</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3894</v>
+        <v>0.0507</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5318</v>
+        <v>-1.262</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0543</v>
+        <v>0.0174</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4775</v>
+        <v>-1.2794</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1866</v>
@@ -1156,13 +1156,13 @@
         <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4448</v>
+        <v>-0.175</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7345</v>
+        <v>0.3371</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7103</v>
+        <v>-0.5121</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6335</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6767</v>
+        <v>-3.251</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4223</v>
+        <v>-4.8481</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7457</v>
+        <v>1.597</v>
       </c>
       <c r="G10" t="n">
         <v>-5.2735</v>
@@ -1234,13 +1234,13 @@
         <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8534</v>
+        <v>0.279</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0242</v>
+        <v>0.5984</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1708</v>
+        <v>-0.3194</v>
       </c>
       <c r="V10" t="n">
         <v>0.6439</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.735</v>
+        <v>-3.6255</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8733</v>
+        <v>-1.4914</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8616</v>
+        <v>-2.1341</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7599</v>
@@ -1312,13 +1312,13 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5589</v>
+        <v>0.6684</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3726</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1863</v>
+        <v>-0.0862</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9005</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.6143</v>
+        <v>14.16489999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>4.149099999999999</v>
+        <v>4.699600000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>9.465499999999999</v>
+        <v>9.465399999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.831100000000001</v>
+        <v>-1.831099999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-1.831</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0001000000000001</v>
+        <v>0.0001000000000005441</v>
       </c>
       <c r="J12" t="n">
         <v>6.261800000000001</v>
@@ -1372,7 +1372,7 @@
         <v>1.604800000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.092699999999999</v>
+        <v>-8.092700000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-6.488</v>
@@ -1390,10 +1390,10 @@
         <v>23.8234</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2851</v>
+        <v>2.8356</v>
       </c>
       <c r="T12" t="n">
-        <v>3.462</v>
+        <v>4.0122</v>
       </c>
       <c r="U12" t="n">
         <v>-1.1768</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4037</v>
+        <v>4.5014</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3863</v>
+        <v>3.9055</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0174</v>
+        <v>0.5959</v>
       </c>
       <c r="G13" t="n">
         <v>6.0034</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1337</v>
+        <v>-0.036</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8047</v>
+        <v>0.3239</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9384</v>
+        <v>-0.3599</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>E. NAVARRO VALDÉS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.77</v>
+        <v>0.6251</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.545</v>
+        <v>0.6251</v>
       </c>
       <c r="F14" t="n">
-        <v>2.315</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0273</v>
+        <v>0.6251</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0657</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0384</v>
+        <v>0.6251</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9779</v>
+        <v>0.6251</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.728</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7501</v>
+        <v>0.6251</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9505</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6623</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2882</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1797</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9147999999999999</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2649</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDÉS</t>
+          <t>O. FORNER LUCEA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6251</v>
+        <v>0.5821</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6251</v>
+        <v>0.1789</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.4032</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6251</v>
+        <v>0.266</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.3846</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6251</v>
+        <v>-0.1187</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6251</v>
+        <v>0.0417</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6251</v>
+        <v>0.0417</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.2243</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.3846</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.1603</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.1329</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.1373</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.0043</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. FORNER LUCEA</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1873</v>
+        <v>0.448</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0134</v>
+        <v>-1.9296</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2007</v>
+        <v>2.3775</v>
       </c>
       <c r="G16" t="n">
-        <v>0.266</v>
+        <v>-0.0273</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3846</v>
+        <v>-1.0657</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1187</v>
+        <v>1.0384</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0417</v>
+        <v>-0.9779</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-1.728</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0417</v>
+        <v>0.7501</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2243</v>
+        <v>0.9505</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3846</v>
+        <v>0.6623</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1603</v>
+        <v>0.2882</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1833</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2619</v>
+        <v>0.8576</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0551</v>
+        <v>0.5302</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2069</v>
+        <v>0.3275</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>L. JURADO TRAVER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8622</v>
+        <v>-0.7432</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0433</v>
+        <v>-1.396</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9055</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4941</v>
+        <v>-1.797</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2112</v>
+        <v>-0.4284</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7053</v>
+        <v>-1.3686</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0433</v>
+        <v>-1.7297</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0433</v>
+        <v>0.1517</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.8814</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5374</v>
+        <v>-0.0673</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1679</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7053</v>
+        <v>0.5128</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3681</v>
+        <v>0.3207</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.3337</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3681</v>
+        <v>-0.013</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0054</v>
+        <v>-0.8074</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4903</v>
+        <v>-0.2018</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5151</v>
+        <v>-0.6056</v>
       </c>
       <c r="G18" t="n">
         <v>1.6059</v>
@@ -1858,13 +1858,13 @@
         <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.229</v>
+        <v>-0.0309</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.46</v>
+        <v>-0.1715</v>
       </c>
       <c r="U18" t="n">
-        <v>0.231</v>
+        <v>0.1406</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. JURADO TRAVER</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6334</v>
+        <v>-0.8374</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8767</v>
+        <v>0.0433</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2434</v>
+        <v>-0.8807</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.797</v>
+        <v>-0.4941</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4284</v>
+        <v>0.2112</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3686</v>
+        <v>-0.7053</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.7297</v>
+        <v>0.0433</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1517</v>
+        <v>0.0433</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8814</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0673</v>
+        <v>-0.5374</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0.1679</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5128</v>
+        <v>-0.7053</v>
       </c>
       <c r="P19" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5695</v>
+        <v>-0.3433</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1471</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4224</v>
+        <v>-0.3433</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8488</v>
+        <v>-1.3044</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1399</v>
+        <v>-0.1784</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7089</v>
+        <v>-1.1261</v>
       </c>
       <c r="G20" t="n">
         <v>2.2513</v>
@@ -2014,13 +2014,13 @@
         <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2125</v>
+        <v>-0.6682</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2481</v>
+        <v>-0.2865</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9644</v>
+        <v>-0.3816</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8954</v>
+        <v>-2.4976</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7934</v>
+        <v>-1.6972</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.102</v>
+        <v>-0.8004</v>
       </c>
       <c r="G21" t="n">
         <v>0.0492</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8738</v>
+        <v>-0.4761</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.405</v>
+        <v>-0.3088</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4689</v>
+        <v>-0.1673</v>
       </c>
       <c r="V21" t="n">
         <v>0.3115</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1003</v>
+        <v>-3.4776</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4683</v>
+        <v>-2.949</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.632</v>
+        <v>-0.5286</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5188</v>
@@ -2170,13 +2170,13 @@
         <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2957</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6946</v>
+        <v>0.2138</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3989</v>
+        <v>-0.2955</v>
       </c>
       <c r="V22" t="n">
         <v>0.3219</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3492</v>
+        <v>-3.5357</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7331</v>
+        <v>-2.5023</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6162</v>
+        <v>-1.0334</v>
       </c>
       <c r="G23" t="n">
         <v>-0.983</v>
@@ -2248,13 +2248,13 @@
         <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6442</v>
+        <v>0.4578</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2074</v>
+        <v>0.4382</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5632</v>
+        <v>0.0196</v>
       </c>
       <c r="V23" t="n">
         <v>-1.9109</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9059</v>
+        <v>-4.0035</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.46</v>
+        <v>-3.3639</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4458</v>
+        <v>-0.6397</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1497</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2438</v>
+        <v>0.1461</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1297</v>
+        <v>-0.0335</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3735</v>
+        <v>0.1797</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.6145</v>
+        <v>-11.0502</v>
       </c>
       <c r="E25" t="n">
         <v>-9.465399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.149</v>
+        <v>-1.5852</v>
       </c>
       <c r="G25" t="n">
         <v>1.831</v>
       </c>
       <c r="H25" t="n">
-        <v>1.830999999999998</v>
+        <v>1.831</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="J25" t="n">
         <v>8.092599999999999</v>
@@ -2386,7 +2386,7 @@
         <v>1.6047</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.2617</v>
+        <v>-6.261699999999999</v>
       </c>
       <c r="N25" t="n">
         <v>-4.6569</v>
@@ -2404,13 +2404,13 @@
         <v>10.9954</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.2851</v>
+        <v>0.279</v>
       </c>
       <c r="T25" t="n">
-        <v>1.1765</v>
+        <v>1.1768</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.4618</v>
+        <v>-0.8975</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3324000000000003</v>
